--- a/data/imm_data.xlsx
+++ b/data/imm_data.xlsx
@@ -16714,12 +16714,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ILP Portfolio Solutions - Discretion Portfolio 01</t>
+          <t>ILP Discretion Portfolio 01</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -16860,12 +16860,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Entity B Portfolio Solutions - Discretion Portfolio 02</t>
+          <t>Entity B Discretion Portfolio 02</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -17006,12 +17006,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Entity A Portfolio Solutions - Discretion Portfolio 03</t>
+          <t>Entity A Discretion Portfolio 03</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -17152,12 +17152,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ILP Portfolio Solutions - Discretion Portfolio 04</t>
+          <t>ILP Discretion Portfolio 04</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -17298,12 +17298,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Entity A Portfolio Solutions - Discretion Portfolio 05</t>
+          <t>Entity A Discretion Portfolio 05</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -17444,12 +17444,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Entity A Portfolio Solutions - Discretion Portfolio 06</t>
+          <t>Entity A Discretion Portfolio 06</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -17590,12 +17590,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>GA Portfolio Solutions - Discretion Portfolio 07</t>
+          <t>GA Discretion Portfolio 07</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -17736,12 +17736,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>GA Portfolio Solutions - Discretion Portfolio 08</t>
+          <t>GA Discretion Portfolio 08</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -17882,12 +17882,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>GA Portfolio Solutions - Discretion Portfolio 09</t>
+          <t>GA Discretion Portfolio 09</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -18028,12 +18028,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>GA Portfolio Solutions - Discretion Portfolio 10</t>
+          <t>GA Discretion Portfolio 10</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -34234,12 +34234,12 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>ILP Portfolio Solutions - Discretion Portfolio 01</t>
+          <t>ILP Discretion Portfolio 01</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -34380,12 +34380,12 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Entity B Portfolio Solutions - Discretion Portfolio 02</t>
+          <t>Entity B Discretion Portfolio 02</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -34526,12 +34526,12 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Entity A Portfolio Solutions - Discretion Portfolio 03</t>
+          <t>Entity A Discretion Portfolio 03</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -34672,12 +34672,12 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>ILP Portfolio Solutions - Discretion Portfolio 04</t>
+          <t>ILP Discretion Portfolio 04</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -34818,12 +34818,12 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Entity A Portfolio Solutions - Discretion Portfolio 05</t>
+          <t>Entity A Discretion Portfolio 05</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -34964,12 +34964,12 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Entity A Portfolio Solutions - Discretion Portfolio 06</t>
+          <t>Entity A Discretion Portfolio 06</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -35110,12 +35110,12 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>GA Portfolio Solutions - Discretion Portfolio 07</t>
+          <t>GA Discretion Portfolio 07</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -35256,12 +35256,12 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>GA Portfolio Solutions - Discretion Portfolio 08</t>
+          <t>GA Discretion Portfolio 08</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -35402,12 +35402,12 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>GA Portfolio Solutions - Discretion Portfolio 09</t>
+          <t>GA Discretion Portfolio 09</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -35548,12 +35548,12 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>GA Portfolio Solutions - Discretion Portfolio 10</t>
+          <t>GA Discretion Portfolio 10</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -51754,12 +51754,12 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>ILP Portfolio Solutions - Discretion Portfolio 01</t>
+          <t>ILP Discretion Portfolio 01</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -51900,12 +51900,12 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Entity B Portfolio Solutions - Discretion Portfolio 02</t>
+          <t>Entity B Discretion Portfolio 02</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -52046,12 +52046,12 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Entity A Portfolio Solutions - Discretion Portfolio 03</t>
+          <t>Entity A Discretion Portfolio 03</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -52192,12 +52192,12 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>ILP Portfolio Solutions - Discretion Portfolio 04</t>
+          <t>ILP Discretion Portfolio 04</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -52338,12 +52338,12 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Entity A Portfolio Solutions - Discretion Portfolio 05</t>
+          <t>Entity A Discretion Portfolio 05</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -52484,12 +52484,12 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Entity A Portfolio Solutions - Discretion Portfolio 06</t>
+          <t>Entity A Discretion Portfolio 06</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -52630,12 +52630,12 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>GA Portfolio Solutions - Discretion Portfolio 07</t>
+          <t>GA Discretion Portfolio 07</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -52776,12 +52776,12 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>GA Portfolio Solutions - Discretion Portfolio 08</t>
+          <t>GA Discretion Portfolio 08</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -52922,12 +52922,12 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>GA Portfolio Solutions - Discretion Portfolio 09</t>
+          <t>GA Discretion Portfolio 09</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -53068,12 +53068,12 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>GA Portfolio Solutions - Discretion Portfolio 10</t>
+          <t>GA Discretion Portfolio 10</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>5a. Portfolio Solutions - Discretion</t>
+          <t>5a. Discretion</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
